--- a/人事情報_統合.xlsx
+++ b/人事情報_統合.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sekishinkai-my.sharepoint.com/personal/ko-suzuki_sekishinkai_onmicrosoft_com/Documents/デスクトップ/人事情報（※サイト表示用フォルダ）/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{CAF724C9-61F5-4C89-AE46-9DD2EB6E4A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7A5195B-563F-4F55-835E-1A78FA3A7346}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{CAF724C9-61F5-4C89-AE46-9DD2EB6E4A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED17C410-48B6-429C-B35E-41CC05A124EF}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="3015" windowWidth="17865" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="17865" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統合" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="249">
   <si>
     <t>年度</t>
   </si>
@@ -620,9 +620,6 @@
   </si>
   <si>
     <t>武藤 美智代</t>
-  </si>
-  <si>
-    <t>立川介護老人保健施設わかば主任</t>
   </si>
   <si>
     <t>海老澤 有華</t>
@@ -777,6 +774,14 @@
     <rPh sb="0" eb="2">
       <t>マスダ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>立川訪問看護ステーションわかば</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>立川訪問看護ステーションわかば主任</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -863,6 +868,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1196,7 +1205,7 @@
         <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F2" t="s">
         <v>74</v>
@@ -1216,7 +1225,7 @@
         <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s">
         <v>77</v>
@@ -1236,7 +1245,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
@@ -1256,7 +1265,7 @@
         <v>66</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -1516,7 +1525,7 @@
         <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F18" t="s">
         <v>61</v>
@@ -1636,7 +1645,7 @@
         <v>81</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
@@ -1656,7 +1665,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F25" t="s">
         <v>70</v>
@@ -1676,7 +1685,7 @@
         <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F26" t="s">
         <v>80</v>
@@ -1787,7 +1796,7 @@
         <v>2023</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -2610,13 +2619,13 @@
         <v>2022</v>
       </c>
       <c r="B73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E73" t="s">
         <v>192</v>
@@ -2670,7 +2679,7 @@
         <v>2022</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -2682,7 +2691,7 @@
         <v>195</v>
       </c>
       <c r="F76" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.15">
@@ -2696,13 +2705,13 @@
         <v>18</v>
       </c>
       <c r="D77" t="s">
+        <v>200</v>
+      </c>
+      <c r="E77" t="s">
         <v>201</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>202</v>
-      </c>
-      <c r="F77" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -2716,13 +2725,13 @@
         <v>18</v>
       </c>
       <c r="D78" t="s">
+        <v>203</v>
+      </c>
+      <c r="E78" t="s">
         <v>204</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>205</v>
-      </c>
-      <c r="F78" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -2730,19 +2739,19 @@
         <v>2022</v>
       </c>
       <c r="B79" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" t="s">
         <v>207</v>
       </c>
-      <c r="C79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
+        <v>204</v>
+      </c>
+      <c r="F79" t="s">
         <v>208</v>
-      </c>
-      <c r="E79" t="s">
-        <v>205</v>
-      </c>
-      <c r="F79" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -2756,13 +2765,13 @@
         <v>18</v>
       </c>
       <c r="D80" t="s">
+        <v>209</v>
+      </c>
+      <c r="E80" t="s">
         <v>210</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>211</v>
-      </c>
-      <c r="F80" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -2776,13 +2785,13 @@
         <v>18</v>
       </c>
       <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" t="s">
+        <v>210</v>
+      </c>
+      <c r="F81" t="s">
         <v>213</v>
-      </c>
-      <c r="E81" t="s">
-        <v>211</v>
-      </c>
-      <c r="F81" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -2796,13 +2805,13 @@
         <v>9</v>
       </c>
       <c r="D82" t="s">
+        <v>214</v>
+      </c>
+      <c r="E82" t="s">
         <v>215</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>216</v>
-      </c>
-      <c r="F82" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -2816,10 +2825,10 @@
         <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E83" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F83" t="s">
         <v>109</v>
@@ -2836,13 +2845,13 @@
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -2856,13 +2865,13 @@
         <v>9</v>
       </c>
       <c r="D85" t="s">
+        <v>218</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F85" t="s">
         <v>219</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F85" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2879,10 +2888,10 @@
         <v>39</v>
       </c>
       <c r="E86" t="s">
+        <v>221</v>
+      </c>
+      <c r="F86" t="s">
         <v>222</v>
-      </c>
-      <c r="F86" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2896,13 +2905,13 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
+        <v>223</v>
+      </c>
+      <c r="E87" t="s">
+        <v>221</v>
+      </c>
+      <c r="F87" t="s">
         <v>224</v>
-      </c>
-      <c r="E87" t="s">
-        <v>222</v>
-      </c>
-      <c r="F87" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2916,13 +2925,13 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
+        <v>225</v>
+      </c>
+      <c r="E88" t="s">
+        <v>221</v>
+      </c>
+      <c r="F88" t="s">
         <v>226</v>
-      </c>
-      <c r="E88" t="s">
-        <v>222</v>
-      </c>
-      <c r="F88" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2936,13 +2945,13 @@
         <v>18</v>
       </c>
       <c r="D89" t="s">
+        <v>227</v>
+      </c>
+      <c r="E89" t="s">
+        <v>221</v>
+      </c>
+      <c r="F89" t="s">
         <v>228</v>
-      </c>
-      <c r="E89" t="s">
-        <v>222</v>
-      </c>
-      <c r="F89" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2956,13 +2965,13 @@
         <v>18</v>
       </c>
       <c r="D90" t="s">
+        <v>229</v>
+      </c>
+      <c r="E90" t="s">
+        <v>221</v>
+      </c>
+      <c r="F90" t="s">
         <v>230</v>
-      </c>
-      <c r="E90" t="s">
-        <v>222</v>
-      </c>
-      <c r="F90" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2976,13 +2985,13 @@
         <v>18</v>
       </c>
       <c r="D91" t="s">
+        <v>231</v>
+      </c>
+      <c r="E91" t="s">
+        <v>221</v>
+      </c>
+      <c r="F91" t="s">
         <v>232</v>
-      </c>
-      <c r="E91" t="s">
-        <v>222</v>
-      </c>
-      <c r="F91" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2996,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F92" t="s">
         <v>191</v>
@@ -3010,19 +3019,19 @@
         <v>2021</v>
       </c>
       <c r="B93" t="s">
+        <v>234</v>
+      </c>
+      <c r="C93" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" t="s">
         <v>235</v>
       </c>
-      <c r="C93" t="s">
-        <v>18</v>
-      </c>
-      <c r="D93" t="s">
-        <v>236</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F93" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
